--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -51,6 +51,7 @@
     <sheet name="magapoke_2026-08-05" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="magapoke_2026-08-12" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="magapoke_2026-08-19" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="magapoke_2026-08-26" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22476,6 +22477,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>千仙戦記</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>キラーシッター</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -52,6 +52,7 @@
     <sheet name="magapoke_2026-08-12" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="magapoke_2026-08-19" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="magapoke_2026-08-26" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="magapoke_2026-09-02" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22753,6 +22754,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>辺境の薬師、都でSランク冒険者となる～英雄村の少年がチート薬で無自覚無双〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>南海トラフ巨大地震</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -53,6 +53,7 @@
     <sheet name="magapoke_2026-08-19" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="magapoke_2026-08-26" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="magapoke_2026-09-02" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="magapoke_2026-09-09" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23030,6 +23031,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -54,6 +54,7 @@
     <sheet name="magapoke_2026-08-26" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="magapoke_2026-09-02" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="magapoke_2026-09-09" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="magapoke_2026-09-16" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23307,6 +23308,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>デッドアカウント</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -55,6 +55,7 @@
     <sheet name="magapoke_2026-09-02" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="magapoke_2026-09-09" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="magapoke_2026-09-16" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="magapoke_2026-09-23" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23584,6 +23585,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>排水溝につまったスライムを日々かたづけるだけの底辺職、なぜか実力者たちの熱い視線を集めてしまう</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -56,6 +56,7 @@
     <sheet name="magapoke_2026-09-09" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="magapoke_2026-09-16" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="magapoke_2026-09-23" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="magapoke_2026-09-30" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24887,6 +24888,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>排水溝につまったスライムを日々かたづけるだけの底辺職、なぜか実力者たちの熱い視線を集めてしまう</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -57,6 +57,7 @@
     <sheet name="magapoke_2026-09-16" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="magapoke_2026-09-23" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="magapoke_2026-09-30" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="magapoke_2026-10-07" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25164,6 +25165,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>島耕作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>冰剣の魔術師が世界を統べる〜世界最強の魔術師である少年は、魔術学院に入学する〜</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -58,6 +58,7 @@
     <sheet name="magapoke_2026-09-23" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="magapoke_2026-09-30" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="magapoke_2026-10-07" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="magapoke_2026-10-14" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25441,6 +25442,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>排水溝につまったスライムを日々かたづけるだけの底辺職、なぜか実力者たちの熱い視線を集めてしまう</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で"最強"なのがバレまくる。～老害どもにはいい加減愛想が尽きました～</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>殺し屋の営業術</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏　～パーティ事情で付与術士をやっていた剣士、万能へと至る～</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -59,6 +59,7 @@
     <sheet name="magapoke_2026-09-30" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="magapoke_2026-10-07" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="magapoke_2026-10-14" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="magapoke_2026-10-21" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25718,6 +25719,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒猫と魔女の教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥～生まれ変わって今更やり直す2度目の学院生活～</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>殺し屋の営業術</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>となりの黒川さん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -60,6 +60,7 @@
     <sheet name="magapoke_2026-10-07" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="magapoke_2026-10-14" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="magapoke_2026-10-21" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="magapoke_2026-10-28" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25995,6 +25996,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア～クソゲーハンター、神ゲーに挑まんとす～</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ギルティサークル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ハナバス　苔石花江のバスケ論</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東京卍リベンジャーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>イレギュラーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐＆『ざまぁ！』します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>アイドラトリィ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる～弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた～</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>『無刀』のおっさん、実はラスダン攻略済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ダメスキル【自動機能】が覚醒しました～あれ、ギルドのスカウトの皆さん、俺を「いらない」って言ってませんでした？～</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>愛妻の裏アカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ハードワーカー中田</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>君が僕らを悪魔と呼んだ頃</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>K-9~警視庁公安部公安第9課異能対策係~</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>食糧人類-Starving Anonymous-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>殺し屋の営業術</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
